--- a/光伏配储项目/电价数据/2026/群星站.xlsx
+++ b/光伏配储项目/电价数据/2026/群星站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.52961</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.13404</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.62673</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.92265</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.7541100000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6782100000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45542</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42271</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40829</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42469</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42257</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44508</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.44136</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.66691</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.5498999999999999</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.42055</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.23497</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.46002</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.48584</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.20528</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.28319</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.66414</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.66328</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.63489</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.09719</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.43483</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.23218</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.26508</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.42974</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.68459</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.70941</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.22966</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.48881</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.25943</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.5579400000000001</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.5504199999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.6888099999999999</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.63627</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.66674</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.88182</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.23928</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.36366</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.50625</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.6032799999999999</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.06816</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.8613200000000001</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.7300800000000001</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.8621799999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.03255</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.8548</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.4618</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.54089</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.22456</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.57814</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.9399500000000001</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.10521</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.96009</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.24301</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.05436</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.0589</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.02145</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.67374</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47937</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4222</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.00153</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9184099999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9834700000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5225</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53577</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47244</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42104</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5386299999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.72058</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7240700000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45292</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.75314</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.87738</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.5170399999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.66857</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.73268</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.5882000000000001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.5758799999999999</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.46871</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.56613</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.90838</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.93849</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.22309</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.8672799999999999</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.06365</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.7739</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.73712</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.9164099999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.7665</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.18241</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.44789</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.5431699999999999</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.45501</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.82469</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.7777500000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.8135399999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.75393</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.65304</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.6733300000000001</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.2552</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.78416</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.8989</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.9438</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.75618</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.1694</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.38041</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.31294</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.29916</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.39721</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.38075</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.55245</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.01128</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.10393</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.59974</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.8123400000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.6091799999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.58593</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.74298</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44075</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3335</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51552</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.44311</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.52862</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.4209</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44968</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39327</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47338</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44412</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39685</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.5741799999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.5594</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.67598</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.56308</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.5227200000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.5541699999999999</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.44195</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.65023</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.7875599999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.09165</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.55226</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.87087</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.1208</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.68444</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.71136</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.61412</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7091799999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.82631</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.80664</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.59173</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.41129</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.45522</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.79657</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.75964</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.8348</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.26037</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.97815</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.02973</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.7938099999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.7287400000000001</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.05818</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.12676</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.03785</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.98656</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.9290499999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.9781</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.9170900000000001</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.32932</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.8136</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.32075</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.8095599999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.8304400000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8165</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.88405</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.8142200000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.91251</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.77777</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.6149</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.6058</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.47262</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.8022699999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.55086</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44753</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.48746</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.5224099999999999</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.50519</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46653</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.5237999999999999</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.47904</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.5658099999999999</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.76855</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.7996599999999999</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.57072</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.8321900000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.8960900000000001</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.5375599999999999</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.62999</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.65723</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.9023300000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.8132</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.00275</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.74714</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.7255900000000001</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.46049</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.54242</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.45013</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.46476</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.70775</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.87921</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.6295299999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.67011</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.72973</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.68175</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.65891</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.62286</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.77136</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.79327</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.50829</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.71812</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.77544</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.73503</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.54288</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.6852</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.7303500000000001</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.67267</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.7490800000000001</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.82709</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.8345900000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.83327</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.83948</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.34521</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.78586</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.75215</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.70024</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.7475499999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.7739299999999999</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.77283</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.74474</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.7055499999999999</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.52723</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.4069700000000001</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.5337499999999999</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30757</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.49643</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.44146</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.29447</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.23946</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.24762</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.24706</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.16899</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.16438</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.19401</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.16511</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.22214</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.15074</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.16252</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.27447</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.2321</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26843</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.11679</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.27925</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.11349</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.26892</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.20531</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.20435</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.19844</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.22154</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.1688</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.19329</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.16873</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.16277</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.16346</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.10386</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.11705</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.13968</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.23551</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.45394</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.40846</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.45884</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.41138</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40985</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.30574</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.92262</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.67252</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.7055</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.50366</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.49124</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.19128</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.11017</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04445</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04447</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04189</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.004030000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.17849</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.03591</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.09891</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.03292</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04283</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04491</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0448</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.02253</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04231</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04458</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04209</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04236</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.10909</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04448</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04248</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.10979</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.10931</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04988</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.11114</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.11751</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.12236</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.12313</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.12474</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33599</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.36944</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.29607</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.23172</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.22293</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.2603</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.29839</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.5365700000000001</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.6294099999999999</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.50428</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.47743</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.53716</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.57394</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.69489</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.44925</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.57787</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.56814</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.6545700000000001</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.45685</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.42359</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.53285</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.52388</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.49163</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.49855</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47992</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.62294</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79503</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7059</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.6252000000000001</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.90577</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.17394</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.67648</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.18892</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.15814</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.57785</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.59275</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.15524</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.84635</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.5176</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.14765</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.40852</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.56804</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.25462</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.66834</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8047000000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7875800000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7884800000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8785700000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88107</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50604</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41649</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46468</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22359</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63925</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54244</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5022300000000001</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42606</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43998</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42052</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38856</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59299</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43205</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5893999999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.72102</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.5276799999999999</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.56116</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.5177200000000001</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.1745</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.81153</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.07401</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.05277</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.03062</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.58877</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.43667</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.47819</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.65171</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.60897</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.49564</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.4541</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.68628</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.58185</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.08459</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.48069</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.49007</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.46048</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.45727</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.49719</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.4553</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.47351</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.48494</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.45028</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.47254</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.46975</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.46436</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.48221</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.5448200000000001</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.54252</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.48604</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.48262</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.49832</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.47988</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.4704700000000001</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.46048</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.46517</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.45205</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45215</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41475</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35314</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95577</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47632</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40684</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4789</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54125</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.40956</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.51042</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.43867</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.46704</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.5181</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.60061</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.7156</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.5829299999999999</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.66989</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.57994</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.64211</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.58761</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.48642</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.56187</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.65587</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.6063500000000001</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.92337</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.6251</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.51028</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.76916</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.56132</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.5679</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.47156</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.9347300000000001</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.5349400000000001</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.50219</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.42909</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.42223</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.8468</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.02503</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.63133</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.30504</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70355</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7952899999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64975</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.65189</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.55835</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.38713</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.7519</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.6321</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.48243</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.8945299999999999</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.50497</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.90007</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.21855</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.95524</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.62027</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.43297</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.02867</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.93111</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.70461</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.69074</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.6643</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.75866</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.04512</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.8616699999999999</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.43741</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.56972</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.8402500000000001</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.51652</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.6948799999999999</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.66735</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.5939500000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.62305</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.61085</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.7251000000000001</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.72504</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.61038</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.7380099999999999</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.9525399999999999</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.69148</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.6792100000000001</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.7503500000000001</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.6489400000000001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.6642899999999999</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.92945</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.67026</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.6721</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.73258</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.6334099999999999</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.62103</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.13821</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.7824500000000001</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.2912</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.03394</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.7078300000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.6967899999999999</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.58647</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3247</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.72286</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23596</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.24426</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.26444</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.68249</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.6442100000000001</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.21934</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.23297</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.26703</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.25134</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.26117</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.26933</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.25583</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.28591</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.23718</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.49571</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44796</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43926</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40253</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54231</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46867</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.6114299999999999</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.27921</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27149</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.27221</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.47353</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.43898</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.43444</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.50786</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.65101</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.61938</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.5164800000000001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.38629</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.48412</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.5593400000000001</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.6405</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.6383799999999999</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.5116499999999999</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39784</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.45939</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.49503</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.5900299999999999</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.59478</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.5834900000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.58594</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.81491</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.80452</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.53411</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.6429600000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.9446100000000001</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.5698799999999999</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.9288099999999999</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.80883</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.80155</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.86893</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.27677</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.6462</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.9623999999999999</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.62417</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.62651</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.57675</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.80113</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.78422</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.8176100000000001</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.8309500000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.8260700000000001</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.80324</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.82769</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.66492</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.86085</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.00594</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.94217</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.9336599999999999</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.85775</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.86549</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.8735700000000001</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.90785</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.57765</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.62198</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.85158</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.85994</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.8538600000000001</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.30348</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.93325</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.24993</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.88346</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.99163</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.5295599999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.46246</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.65353</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.35688</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.89436</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.60512</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31541</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.6230399999999999</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.61646</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.62095</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.48966</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.39707</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2820299999999999</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.54916</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.75112</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.6570199999999999</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.55604</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.49094</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.42143</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.48852</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.86248</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.49407</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6519400000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83084</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47176</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41073</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.5079900000000001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.26876</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.47743</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.69836</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.12002</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27625</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.18829</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.39349</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.23919</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.26027</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.45405</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.6289199999999999</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.83051</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.26641</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.68852</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.05928</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.50525</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.68759</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.46265</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.70978</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.6592</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.47853</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.13644</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.65277</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.8089400000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.89712</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.13035</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.18103</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48687</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.79813</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.9305399999999999</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.7889299999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.61505</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.00256</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.84573</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.45389</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40878</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41142</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41834</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5604600000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50057</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45061</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.99022</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.32792</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.43632</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.50691</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.21777</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.18947</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.34146</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.67407</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.66418</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.67877</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.31007</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.32817</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.5678799999999999</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7036100000000001</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.57041</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.64151</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.15785</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.55022</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.40353</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.12299</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.06299</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.9806</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.96358</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.65652</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.63967</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.91577</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.41784</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.46569</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.47525</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.5754900000000001</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.77504</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.5452400000000001</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.67932</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.53001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.6960499999999999</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.70614</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.07492</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.03032</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.8204</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.8215399999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.90823</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.94816</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.2712</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.50471</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.35335</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.13593</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.78807</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.72364</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.57487</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.48691</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.83333</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.98738</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.74007</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47814</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47151</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.96596</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6021599999999999</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48939</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45805</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44835</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45768</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.42255</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.43452</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4747</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.54573</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.52408</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.53008</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.7825800000000001</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.76493</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.04465</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.05659</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.70768</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.75425</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.7649600000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.43433</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1.76081</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.43541</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.42699</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.45316</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.45912</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.43313</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.48383</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.46484</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.51346</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.58989</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.71748</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.50247</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43145</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.13678</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.27245</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.21044</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.22804</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.13082</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.22722</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.23947</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.14994</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.27101</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.21778</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25696</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28005</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.48548</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.42771</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43083</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.41606</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.46596</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.43841</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35168</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.52273</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19061</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24072</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.18788</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.17819</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.13709</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.12259</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.23097</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.12434</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.13556</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.11803</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.17604</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.20076</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.16408</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.13109</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.12354</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.17118</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.11411</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.13002</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.11431</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.22259</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.11344</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.11984</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.11347</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.12111</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.12274</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.12076</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.20231</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.15284</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.24125</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.25266</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.57185</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.27766</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.25519</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.73138</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.65485</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.5414</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.47857</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.27819</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.8108300000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.81379</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.92863</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.77488</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.5596599999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.7819199999999999</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.23261</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.25076</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.27969</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.18219</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.10902</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.22693</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28251</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.12851</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.54359</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.26387</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.62627</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.09903</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.53716</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.48548</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.7857999999999999</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.6399900000000001</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.64555</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.6508999999999999</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.65608</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.75864</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.50322</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.6834199999999999</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.53085</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.7084400000000001</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.61073</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.02955</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.02543</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.06412</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.36838</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.10299</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.15729</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.43895</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.79513</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.6832999999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.72953</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.72768</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.96893</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.83639</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.66514</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.5273</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3344</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.44944</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.57041</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.43875</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.5314099999999999</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.43753</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.8968700000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.7288</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.65418</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.60737</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.49364</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.57324</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.51303</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.48041</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.15076</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.6222799999999999</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.8028200000000001</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.7153099999999999</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.8056599999999999</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.05419</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.04884</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.7264299999999999</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.74422</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.54374</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.42292</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.42428</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.47413</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.20825</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.42675</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.42187</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.47719</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.8896000000000001</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.56051</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.41182</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.44136</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.44449</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.43411</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.45036</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.50619</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.7672100000000001</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.73497</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.50601</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.91203</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.6177699999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.54853</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.76924</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.6534</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.44313</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.44626</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.43638</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33704</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40728</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.49509</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5795</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.51397</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.7243999999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.96093</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.21828</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.44438</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.56625</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.6794199999999999</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.71762</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.66523</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.6381100000000001</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.6719400000000001</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.6506799999999999</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.63967</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.64285</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.96811</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.42973</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.63374</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.45782</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.65116</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.6565700000000001</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.47042</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.6384</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.54448</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.64964</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.64213</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.65795</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.85451</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.99595</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.0185</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.06569</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.13236</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.11545</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.18533</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.19779</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.17562</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.8795599999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.77611</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.74614</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4763</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.9245800000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.7122999999999999</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7932899999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.68244</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.6493</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.63262</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.6238400000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.60868</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42417</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6844</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5329199999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45845</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.53547</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.59524</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.56157</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.6391100000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.45431</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.66612</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.57348</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.6659700000000001</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.63022</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.63459</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.5450199999999999</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.30915</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.34736</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.71797</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.5602200000000001</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.71737</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.64638</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.7254299999999999</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.70821</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.70833</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.9868400000000001</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.00571</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.6851900000000001</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.48331</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.52927</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.2583</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.56257</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.64215</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.62651</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.6221</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.0043</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.00649</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.36156</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.02736</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.3652</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.34682</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.37878</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.13276</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.05732</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.80664</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.7872</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.40775</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.48123</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.25252</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.25359</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.07594</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.39701</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.4877</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.46451</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.01289</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.9019400000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.68437</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.22259</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.2008</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.47757</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.24436</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.24614</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.60725</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.5878</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.56702</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37505</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27076</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.5285599999999999</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.42468</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.50641</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.7304400000000001</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.6011799999999999</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.5309400000000001</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.55735</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.7467</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.7255499999999999</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.91183</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.46147</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.24391</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.94357</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.8819600000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.50682</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.10676</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.41558</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.18393</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.12253</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.50513</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.18095</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.50846</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.6047899999999999</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.49778</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.26607</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.6034700000000001</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.45535</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.73291</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.6183999999999999</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.50745</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.63054</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.5175299999999999</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.65103</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.73225</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.78601</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.65413</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.66599</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.6254999999999999</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.64747</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.65808</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.08738</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.15029</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.00896</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.02803</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.18303</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.9519099999999999</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.96761</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.71678</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.6971900000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.70966</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.7458899999999999</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.74152</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.72297</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.8362200000000001</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.5708</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.5582999999999999</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.50504</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.48679</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.40616</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37531</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.20313</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.7736499999999999</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.80959</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.00475</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.66513</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.43017</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.55753</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.46405</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.5375800000000001</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.5334500000000001</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.50413</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.61502</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.5301900000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.62053</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.03129</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.6213500000000001</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.6630199999999999</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.7473200000000001</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.73673</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.6400399999999999</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.8431900000000001</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.6194</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.01889</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.28188</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.59497</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.55061</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.42556</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.52003</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.6324099999999999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.5297999999999999</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.39072</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.46305</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.06003</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.8489099999999999</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.51289</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.12218</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.7043700000000001</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.69662</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.07471</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.16243</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.9805499999999999</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.7854099999999999</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.73746</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.7551100000000001</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.75913</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.78861</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.78374</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.8017000000000001</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.10246</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.13285</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.20205</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.5032</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.73745</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.7602899999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.73127</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.7823600000000001</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.32189</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.54101</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.8875700000000001</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.5581</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.5349299999999999</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.456</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.8731100000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.57074</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.5728799999999999</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.44204</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.44163</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.42457</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.42745</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.41386</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.42525</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.58272</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.6459199999999999</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.86737</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.63013</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.6406900000000001</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.57474</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>1.02059</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.51335</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.25932</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.49284</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.40468</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.5225599999999999</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.44362</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.72875</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.5872000000000001</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.5949500000000001</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.6256799999999999</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.65188</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.50414</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.49067</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.49552</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.50085</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.5169199999999999</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.57655</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.58675</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.49793</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.57032</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.5934400000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.84333</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.56362</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.5420700000000001</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.5281699999999999</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.49442</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.49654</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.62161</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.61085</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.6295299999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.52674</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.49995</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.45787</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40969</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38406</v>
       </c>
     </row>
   </sheetData>
